--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221019</v>
+        <v>125221020</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711234</v>
+        <v>711303</v>
       </c>
       <c r="R2" t="n">
-        <v>7222403</v>
+        <v>7222198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221020</v>
+        <v>125221019</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711303</v>
+        <v>711234</v>
       </c>
       <c r="R3" t="n">
-        <v>7222198</v>
+        <v>7222403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221020</v>
+        <v>125221019</v>
       </c>
       <c r="B2" t="n">
-        <v>92285</v>
+        <v>92328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711303</v>
+        <v>711234</v>
       </c>
       <c r="R2" t="n">
-        <v>7222198</v>
+        <v>7222403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221019</v>
+        <v>125221020</v>
       </c>
       <c r="B3" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711234</v>
+        <v>711303</v>
       </c>
       <c r="R3" t="n">
-        <v>7222403</v>
+        <v>7222198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221019</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>92484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125221020</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221019</v>
+        <v>125221020</v>
       </c>
       <c r="B2" t="n">
-        <v>92484</v>
+        <v>92440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711234</v>
+        <v>711303</v>
       </c>
       <c r="R2" t="n">
-        <v>7222403</v>
+        <v>7222198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221020</v>
+        <v>125221019</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711303</v>
+        <v>711234</v>
       </c>
       <c r="R3" t="n">
-        <v>7222198</v>
+        <v>7222403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221020</v>
+        <v>125221019</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711303</v>
+        <v>711234</v>
       </c>
       <c r="R2" t="n">
-        <v>7222198</v>
+        <v>7222403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221019</v>
+        <v>125221020</v>
       </c>
       <c r="B3" t="n">
-        <v>92484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711234</v>
+        <v>711303</v>
       </c>
       <c r="R3" t="n">
-        <v>7222403</v>
+        <v>7222198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 52538-2024 artfynd.xlsx
+++ b/artfynd/A 52538-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221019</v>
       </c>
       <c r="B2" t="n">
-        <v>92538</v>
+        <v>92545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125221020</v>
       </c>
       <c r="B3" t="n">
-        <v>92494</v>
+        <v>92501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
